--- a/data/numeric/input/data_59/白班晚班设备运行与环保停工记录.xlsx
+++ b/data/numeric/input/data_59/白班晚班设备运行与环保停工记录.xlsx
@@ -1994,26 +1994,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F10D5C1-7852-482A-B473-39F6D1751963}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A46675B-5F9A-4743-8F44-FE51F3D3ED58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67030973-D2D0-46E0-AEA4-7A03CF098AA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30321065-EC1C-4391-A6BD-AB5A340C0604}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01FBFCD4-0720-4544-834C-9A52D0B859DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF484E07-A237-4411-963C-C0B65577D9B5}"/>
 </file>